--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F707"/>
+  <dimension ref="A1:F708"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20175,27 +20175,27 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>touch_layout_coming_soon</t>
+          <t>steal_instruction_tap_compact</t>
         </is>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Placeholder/fallback text</t>
+          <t>Steal-mode instructional hint shown in the compact top-bar rules pill (replaces the rule name while steal mode is active) — short enough to fit that one-line pill instead of steal_instruction_tap's full two-line wording.</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
         <is>
-          <t>Touch layout coming soon</t>
+          <t>Double-tap to steal a card</t>
         </is>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Diseño táctil próximamente</t>
+          <t>Toca dos veces para robar una carta</t>
         </is>
       </c>
       <c r="F655" t="b">
@@ -20210,26 +20210,26 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>touch_blackjack_title</t>
+          <t>touch_layout_coming_soon</t>
         </is>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Title-case game label</t>
+          <t>Placeholder/fallback text</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Touch layout coming soon</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Diseño táctil próximamente</t>
         </is>
       </c>
       <c r="F656" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="657">
@@ -20240,22 +20240,22 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>touch_blackjack_banner</t>
+          <t>touch_blackjack_title</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>All-caps banner/header label</t>
+          <t>Title-case game label</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>BLACKJACK</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="F657" t="b">
@@ -20270,7 +20270,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>touch_spider_banner</t>
+          <t>touch_blackjack_banner</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
@@ -20280,12 +20280,12 @@
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>SPIDER</t>
+          <t>BLACKJACK</t>
         </is>
       </c>
       <c r="F658" t="b">
@@ -20300,7 +20300,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>touch_klondike_banner</t>
+          <t>touch_spider_banner</t>
         </is>
       </c>
       <c r="C659" t="inlineStr">
@@ -20310,12 +20310,12 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>KLONDIKE</t>
+          <t>SPIDER</t>
         </is>
       </c>
       <c r="F659" t="b">
@@ -20330,7 +20330,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>touch_beecell_banner</t>
+          <t>touch_klondike_banner</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
@@ -20340,12 +20340,12 @@
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>BEECELL</t>
+          <t>KLONDIKE</t>
         </is>
       </c>
       <c r="F660" t="b">
@@ -20355,57 +20355,57 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Chrome</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>debug_banners_menu</t>
+          <t>touch_beecell_banner</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Mac-only dev menu title</t>
+          <t>All-caps banner/header label</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Banners</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Anuncios</t>
+          <t>BEECELL</t>
         </is>
       </c>
       <c r="F661" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>ManageDecksWin</t>
+          <t>Chrome</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>deck_default_name</t>
+          <t>debug_banners_menu</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
+          <t>Mac-only dev menu title</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Banners</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Predeterminado</t>
+          <t>Anuncios</t>
         </is>
       </c>
       <c r="F662" t="b">
@@ -20415,27 +20415,27 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>TouchViewsIOS</t>
+          <t>ManageDecksWin</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>free_play_label</t>
+          <t>deck_default_name</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
+          <t>Windows Manage Decks: display name for the slot-0 (default) deck</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Free Play</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Juego Libre</t>
+          <t>Predeterminado</t>
         </is>
       </c>
       <c r="F663" t="b">
@@ -20450,22 +20450,22 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>touch_choose_photo</t>
+          <t>free_play_label</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
+          <t>iOS Blackjack/Video Poker touch view: credits capsule label in free-play mode</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Choose Photo</t>
+          <t>Free Play</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Elegir Foto</t>
+          <t>Juego Libre</t>
         </is>
       </c>
       <c r="F664" t="b">
@@ -20480,22 +20480,22 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>touch_choose_different_photo</t>
+          <t>touch_choose_photo</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
+          <t>iOS custom-art import sheets: photo picker button, no image chosen yet</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Choose a Different Photo</t>
+          <t>Choose Photo</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Elegir Otra Foto</t>
+          <t>Elegir Foto</t>
         </is>
       </c>
       <c r="F665" t="b">
@@ -20510,22 +20510,22 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>touch_pinch_zoom_reposition</t>
+          <t>touch_choose_different_photo</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: crop editor section header</t>
+          <t>iOS custom-art import sheets: photo picker button, image already chosen</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Pinch to zoom, drag to reposition</t>
+          <t>Choose a Different Photo</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
+          <t>Elegir Otra Foto</t>
         </is>
       </c>
       <c r="F666" t="b">
@@ -20540,22 +20540,22 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>touch_name_field_placeholder</t>
+          <t>touch_pinch_zoom_reposition</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: name TextField placeholder</t>
+          <t>iOS custom-art import sheets: crop editor section header</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Pinch to zoom, drag to reposition</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Nombre</t>
+          <t>Pellizca para hacer zoom, arrastra para reposicionar</t>
         </is>
       </c>
       <c r="F667" t="b">
@@ -20570,22 +20570,22 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>touch_name_already_taken_error</t>
+          <t>touch_name_field_placeholder</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>iOS custom-art import sheets: duplicate-name validation error</t>
+          <t>iOS custom-art import sheets: name TextField placeholder</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>That name is already taken — pick another.</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Ese nombre ya está en uso — elige otro.</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="F668" t="b">
@@ -20600,22 +20600,22 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>touch_enabled_toggle</t>
+          <t>touch_name_already_taken_error</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
+          <t>iOS custom-art import sheets: duplicate-name validation error</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Enabled</t>
+          <t>That name is already taken — pick another.</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Activado</t>
+          <t>Ese nombre ya está en uso — elige otro.</t>
         </is>
       </c>
       <c r="F669" t="b">
@@ -20630,22 +20630,22 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>card_back_default_name</t>
+          <t>touch_enabled_toggle</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Auto-filled base name for a new custom card back before the user renames it (appended with ' N' for the 2nd, 3rd, ... duplicate)</t>
+          <t>iOS custom face-card-art import sheet: Enabled toggle label</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Default</t>
+          <t>Enabled</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Predeterminado</t>
+          <t>Activado</t>
         </is>
       </c>
       <c r="F670" t="b">
@@ -20660,22 +20660,22 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>add_photo_short</t>
+          <t>card_back_default_name</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Caption on the iOS Themes sheet Background grid's Add tile (imports a photo, unlike Card Back/Face Art's plain "Add")</t>
+          <t>Auto-filled base name for a new custom card back before the user renames it (appended with ' N' for the 2nd, 3rd, ... duplicate)</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Add Photo</t>
+          <t>Default</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Añadir Foto</t>
+          <t>Predeterminado</t>
         </is>
       </c>
       <c r="F671" t="b">
@@ -20690,22 +20690,22 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>felt_custom_short</t>
+          <t>add_photo_short</t>
         </is>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Caption on the iOS Themes sheet Background grid's Custom Felt tile — shorter than feltCustomColor ("Custom Felt Color") so it fits the narrow tile without truncating</t>
+          <t>Caption on the iOS Themes sheet Background grid's Add tile (imports a photo, unlike Card Back/Face Art's plain "Add")</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Custom Felt</t>
+          <t>Add Photo</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Fieltro Personalizado</t>
+          <t>Añadir Foto</t>
         </is>
       </c>
       <c r="F672" t="b">
@@ -20720,22 +20720,22 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>stat_position_top</t>
+          <t>felt_custom_short</t>
         </is>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Label on the iOS Card Bank stat-filter dropdown for a card's top corner value</t>
+          <t>Caption on the iOS Themes sheet Background grid's Custom Felt tile — shorter than feltCustomColor ("Custom Felt Color") so it fits the narrow tile without truncating</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>Custom Felt</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Arriba</t>
+          <t>Fieltro Personalizado</t>
         </is>
       </c>
       <c r="F673" t="b">
@@ -20750,22 +20750,22 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>stat_position_bottom</t>
+          <t>stat_position_top</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>Label on the iOS Card Bank stat-filter dropdown for a card's bottom corner value</t>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's top corner value</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Abajo</t>
+          <t>Arriba</t>
         </is>
       </c>
       <c r="F674" t="b">
@@ -20780,22 +20780,22 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>stat_position_left</t>
+          <t>stat_position_bottom</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Label on the iOS Card Bank stat-filter dropdown for a card's left corner value</t>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's bottom corner value</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Bottom</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Izquierda</t>
+          <t>Abajo</t>
         </is>
       </c>
       <c r="F675" t="b">
@@ -20810,22 +20810,22 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>stat_position_right</t>
+          <t>stat_position_left</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Label on the iOS Card Bank stat-filter dropdown for a card's right corner value</t>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's left corner value</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Left</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Derecha</t>
+          <t>Izquierda</t>
         </is>
       </c>
       <c r="F676" t="b">
@@ -20840,22 +20840,22 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>stat_filter_any</t>
+          <t>stat_position_right</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Default/unset option in each iOS Card Bank stat-filter dropdown (matches any value)</t>
+          <t>Label on the iOS Card Bank stat-filter dropdown for a card's right corner value</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Right</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Cualquiera</t>
+          <t>Derecha</t>
         </is>
       </c>
       <c r="F677" t="b">
@@ -20870,22 +20870,22 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>stat_sudden_death_count_ios</t>
+          <t>stat_filter_any</t>
         </is>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>iOS Honeycomb stats sheet label for suddenDeathCount — plainer than mac's thematic "Most Swarms to the Death", matching iOS's literal stat-label style</t>
+          <t>Default/unset option in each iOS Card Bank stat-filter dropdown (matches any value)</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Most Swarms to the Death</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Más Enjambres a Muerte</t>
+          <t>Cualquiera</t>
         </is>
       </c>
       <c r="F678" t="b">
@@ -20900,22 +20900,22 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>stat_fallen_aces_ios</t>
+          <t>stat_sudden_death_count_ios</t>
         </is>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>iOS Honeycomb stats sheet label for fallenAces — plainer than mac's thematic "Queen's Falls", matching iOS's literal stat-label style</t>
+          <t>iOS Honeycomb stats sheet label for suddenDeathCount — plainer than mac's thematic "Most Swarms to the Death", matching iOS's literal stat-label style</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>Queen's Falls</t>
+          <t>Most Swarms to the Death</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Caídas de la Reina</t>
+          <t>Más Enjambres a Muerte</t>
         </is>
       </c>
       <c r="F679" t="b">
@@ -20925,27 +20925,27 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>TouchViewsIOS</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>rule_state_auto</t>
+          <t>stat_fallen_aces_ios</t>
         </is>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Unified rule-list per-row state control, Mac/iOS/Windows</t>
+          <t>iOS Honeycomb stats sheet label for fallenAces — plainer than mac's thematic "Queen's Falls", matching iOS's literal stat-label style</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Queen's Falls</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>Caídas de la Reina</t>
         </is>
       </c>
       <c r="F680" t="b">
@@ -20960,7 +20960,7 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>rule_state_pick</t>
+          <t>rule_state_auto</t>
         </is>
       </c>
       <c r="C681" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Jugar</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="F681" t="b">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>rule_state_ban</t>
+          <t>rule_state_pick</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
@@ -21000,12 +21000,12 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Ban</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Vetar</t>
+          <t>Jugar</t>
         </is>
       </c>
       <c r="F682" t="b">
@@ -21020,22 +21020,22 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>rules_selected_count_fmt</t>
+          <t>rule_state_ban</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Unified rule-list selection counter, Mac/iOS/Windows</t>
+          <t>Unified rule-list per-row state control, Mac/iOS/Windows</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>%d of 4 selected</t>
+          <t>Ban</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>%d de 4 seleccionadas</t>
+          <t>Vetar</t>
         </is>
       </c>
       <c r="F683" t="b">
@@ -21045,27 +21045,27 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>out_of_credits_toast</t>
+          <t>rules_selected_count_fmt</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Toast shown when the player runs out of credits, reused Blackjack/Video Poker</t>
+          <t>Unified rule-list selection counter, Mac/iOS/Windows</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Out of Credits!</t>
+          <t>%d of 4 selected</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>¡Sin créditos!</t>
+          <t>%d de 4 seleccionadas</t>
         </is>
       </c>
       <c r="F684" t="b">
@@ -21075,27 +21075,27 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Blackjack</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>btn_clear_short</t>
+          <t>out_of_credits_toast</t>
         </is>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Short "Clear" label for Blackjack landscape betting grid (fits one line at that button width)</t>
+          <t>Toast shown when the player runs out of credits, reused Blackjack/Video Poker</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Out of Credits!</t>
         </is>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Borrar</t>
+          <t>¡Sin créditos!</t>
         </is>
       </c>
       <c r="F685" t="b">
@@ -21105,27 +21105,27 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Blackjack</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>global_options_section</t>
+          <t>btn_clear_short</t>
         </is>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>iOS Options sheet section header — groups Sound/No Stress Mode/Honey Mode/Hide Hint/Manually Dismiss Banners, separate from the per-game settings section below it</t>
+          <t>Short "Clear" label for Blackjack landscape betting grid (fits one line at that button width)</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Borrar</t>
         </is>
       </c>
       <c r="F686" t="b">
@@ -21135,27 +21135,27 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>hide_bee</t>
+          <t>global_options_section</t>
         </is>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Toggle label, reused across every game's Options on Mac/iOS/Windows</t>
+          <t>iOS Options sheet section header — groups Sound/No Stress Mode/Honey Mode/Hide Hint/Manually Dismiss Banners, separate from the per-game settings section below it</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Hide the Bee</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Ocultar la Abeja</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="F687" t="b">
@@ -21165,27 +21165,27 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Options</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>honey_mode_tooltip</t>
+          <t>hide_bee</t>
         </is>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Tooltip for the Honey Mode toggle</t>
+          <t>Toggle label, reused across every game's Options on Mac/iOS/Windows</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Enables banners and solitaire point animations.</t>
+          <t>Hide the Bee</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Habilita los anuncios y las animaciones de puntos en los solitarios.</t>
+          <t>Ocultar la Abeja</t>
         </is>
       </c>
       <c r="F688" t="b">
@@ -21200,22 +21200,22 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>no_stress_mode_tooltip</t>
+          <t>honey_mode_tooltip</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Tooltip for the No Stress Mode toggle</t>
+          <t>Tooltip for the Honey Mode toggle</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>Pressure-free! No timers, no betting, and Honeycomb chooses your deck for you at random.</t>
+          <t>Enables banners and solitaire point animations.</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>¡Sin presión! Sin temporizadores, sin apuestas, y Honeycomb elige tu mazo al azar.</t>
+          <t>Habilita los anuncios y las animaciones de puntos en los solitarios.</t>
         </is>
       </c>
       <c r="F689" t="b">
@@ -21225,27 +21225,27 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Honeycomb</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>rank_nurse_bee</t>
+          <t>no_stress_mode_tooltip</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Player rank, 10-19 cards collected</t>
+          <t>Tooltip for the No Stress Mode toggle</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Nurse Bee</t>
+          <t>Pressure-free! No timers, no betting, and Honeycomb chooses your deck for you at random.</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Abeja Nodriza</t>
+          <t>¡Sin presión! Sin temporizadores, sin apuestas, y Honeycomb elige tu mazo al azar.</t>
         </is>
       </c>
       <c r="F690" t="b">
@@ -21260,22 +21260,22 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>rank_scout_bee</t>
+          <t>rank_nurse_bee</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Player rank, 20-49 cards collected</t>
+          <t>Player rank, 10-19 cards collected</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>Scout Bee</t>
+          <t>Nurse Bee</t>
         </is>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Abeja Exploradora</t>
+          <t>Abeja Nodriza</t>
         </is>
       </c>
       <c r="F691" t="b">
@@ -21290,22 +21290,22 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>rank_worker_bee</t>
+          <t>rank_scout_bee</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Player rank, 50-99 cards collected</t>
+          <t>Player rank, 20-49 cards collected</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>Worker Bee</t>
+          <t>Scout Bee</t>
         </is>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Abeja Obrera</t>
+          <t>Abeja Exploradora</t>
         </is>
       </c>
       <c r="F692" t="b">
@@ -21320,22 +21320,22 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>rank_guard_bee</t>
+          <t>rank_worker_bee</t>
         </is>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Player rank, 100-149 cards collected</t>
+          <t>Player rank, 50-99 cards collected</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
         <is>
-          <t>Guard Bee</t>
+          <t>Worker Bee</t>
         </is>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Abeja Guardiana</t>
+          <t>Abeja Obrera</t>
         </is>
       </c>
       <c r="F693" t="b">
@@ -21350,22 +21350,22 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>rank_waggle_dancer</t>
+          <t>rank_guard_bee</t>
         </is>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Player rank, 150-199 cards collected</t>
+          <t>Player rank, 100-149 cards collected</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Waggle Dancer</t>
+          <t>Guard Bee</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Abeja Bailarina</t>
+          <t>Abeja Guardiana</t>
         </is>
       </c>
       <c r="F694" t="b">
@@ -21380,22 +21380,22 @@
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>rank_comb_architect</t>
+          <t>rank_waggle_dancer</t>
         </is>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Player rank, 200-299 cards collected</t>
+          <t>Player rank, 150-199 cards collected</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Comb Architect</t>
+          <t>Waggle Dancer</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Arquitecta del Panal</t>
+          <t>Abeja Bailarina</t>
         </is>
       </c>
       <c r="F695" t="b">
@@ -21410,22 +21410,22 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>rank_royal_attendant</t>
+          <t>rank_comb_architect</t>
         </is>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Player rank, 300-399 cards collected</t>
+          <t>Player rank, 200-299 cards collected</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Royal Attendant</t>
+          <t>Comb Architect</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Asistente Real</t>
+          <t>Arquitecta del Panal</t>
         </is>
       </c>
       <c r="F696" t="b">
@@ -21440,22 +21440,22 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>rank_swarm_leader</t>
+          <t>rank_royal_attendant</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Player rank, 400-499 cards collected</t>
+          <t>Player rank, 300-399 cards collected</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Swarm Leader</t>
+          <t>Royal Attendant</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Líder del Enjambre</t>
+          <t>Asistente Real</t>
         </is>
       </c>
       <c r="F697" t="b">
@@ -21470,22 +21470,22 @@
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>rank_hive_monarch</t>
+          <t>rank_swarm_leader</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>Player rank, 500+ cards collected but not the full set</t>
+          <t>Player rank, 400-499 cards collected</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Hive Monarch</t>
+          <t>Swarm Leader</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Monarca de la Colmena</t>
+          <t>Líder del Enjambre</t>
         </is>
       </c>
       <c r="F698" t="b">
@@ -21500,22 +21500,22 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>rank_apiarist</t>
+          <t>rank_hive_monarch</t>
         </is>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Player rank, every card in the collection unlocked</t>
+          <t>Player rank, 500+ cards collected but not the full set</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Apiarist</t>
+          <t>Hive Monarch</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Apicultor</t>
+          <t>Monarca de la Colmena</t>
         </is>
       </c>
       <c r="F699" t="b">
@@ -21525,27 +21525,27 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Honeycomb</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>global_settings_header</t>
+          <t>rank_apiarist</t>
         </is>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Section header, Windows Preferences panel — global (cross-game) settings group</t>
+          <t>Player rank, every card in the collection unlocked</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Global Settings</t>
+          <t>Apiarist</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>Configuración Global</t>
+          <t>Apicultor</t>
         </is>
       </c>
       <c r="F700" t="b">
@@ -21555,27 +21555,27 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>stat_shortest_win_time</t>
+          <t>global_settings_header</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Stat row label, Klondike/Spider/Beecell — shortest winning-game time</t>
+          <t>Section header, Windows Preferences panel — global (cross-game) settings group</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Shortest Win Time</t>
+          <t>Global Settings</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>Tiempo Más Corto de Victoria</t>
+          <t>Configuración Global</t>
         </is>
       </c>
       <c r="F701" t="b">
@@ -21590,22 +21590,22 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>stat_total_paid_out</t>
+          <t>stat_shortest_win_time</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Stat row label, Blackjack/Video Poker</t>
+          <t>Stat row label, Klondike/Spider/Beecell — shortest winning-game time</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Total Paid Out</t>
+          <t>Shortest Win Time</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>Total Pagado</t>
+          <t>Tiempo Más Corto de Victoria</t>
         </is>
       </c>
       <c r="F702" t="b">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>stat_biggest_payout</t>
+          <t>stat_total_paid_out</t>
         </is>
       </c>
       <c r="C703" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Biggest Payout</t>
+          <t>Total Paid Out</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>Mayor Pago</t>
+          <t>Total Pagado</t>
         </is>
       </c>
       <c r="F703" t="b">
@@ -21645,27 +21645,27 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Shared</t>
+          <t>Stats</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>beecell_statistics_title</t>
+          <t>stat_biggest_payout</t>
         </is>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Stats screen title for Beecell</t>
+          <t>Stat row label, Blackjack/Video Poker</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Beecell Statistics</t>
+          <t>Biggest Payout</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>Estadísticas de Beecell</t>
+          <t>Mayor Pago</t>
         </is>
       </c>
       <c r="F704" t="b">
@@ -21675,27 +21675,27 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Casino</t>
+          <t>Shared</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>btn_new_bet</t>
+          <t>beecell_statistics_title</t>
         </is>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Blackjack action button</t>
+          <t>Stats screen title for Beecell</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
         <is>
-          <t>New Bet</t>
+          <t>Beecell Statistics</t>
         </is>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>Nueva Apuesta</t>
+          <t>Estadísticas de Beecell</t>
         </is>
       </c>
       <c r="F705" t="b">
@@ -21710,22 +21710,22 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>btn_rebuy</t>
+          <t>btn_new_bet</t>
         </is>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>Casino action button to rebuy chips</t>
+          <t>Blackjack action button</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
         <is>
-          <t>Rebuy</t>
+          <t>New Bet</t>
         </is>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>Recomprar</t>
+          <t>Nueva Apuesta</t>
         </is>
       </c>
       <c r="F706" t="b">
@@ -21740,25 +21740,55 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
+          <t>btn_rebuy</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Casino action button to rebuy chips</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Rebuy</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Recomprar</t>
+        </is>
+      </c>
+      <c r="F707" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Casino</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
           <t>btn_re_deal</t>
         </is>
       </c>
-      <c r="C707" t="inlineStr">
+      <c r="C708" t="inlineStr">
         <is>
           <t>Blackjack action button to deal again</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr">
+      <c r="D708" t="inlineStr">
         <is>
           <t>Re-Deal</t>
         </is>
       </c>
-      <c r="E707" t="inlineStr">
+      <c r="E708" t="inlineStr">
         <is>
           <t>Repartir</t>
         </is>
       </c>
-      <c r="F707" t="b">
+      <c r="F708" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F708"/>
+  <dimension ref="A1:F720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21789,6 +21789,366 @@
         </is>
       </c>
       <c r="F708" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>pay_table_title</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Video Poker pay-table panel title (Android)</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Pay Table</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Tabla de Pagos</t>
+        </is>
+      </c>
+      <c r="F709" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>delete_item_confirm_fmt</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Confirm-delete dialog title; %@ = item name (Android Themes)</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Delete %@?</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>¿Eliminar %@?</t>
+        </is>
+      </c>
+      <c r="F710" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>theme_asset_delete_body</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Confirm-delete dialog body for a card back/background/face art (Android Themes)</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Any theme using this will fall back to a default. This can't be undone.</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Cualquier tema que use esto volverá a uno predeterminado. Esto no se puede deshacer.</t>
+        </is>
+      </c>
+      <c r="F711" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>import_art_button</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Themes screen top-bar button (Android)</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Import Art</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Importar Arte</t>
+        </is>
+      </c>
+      <c r="F712" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>import_custom_art_title</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Custom art import screen title (Android)</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Import Custom Art</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Importar Arte Personalizado</t>
+        </is>
+      </c>
+      <c r="F713" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>art_type_label</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Custom art import: art-type picker label (Android)</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Art Type</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Tipo de Arte</t>
+        </is>
+      </c>
+      <c r="F714" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>enable_custom_colors_toggle</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Themes: custom card colors toggle (Android)</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Enable Custom Colors</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Activar Colores Personalizados</t>
+        </is>
+      </c>
+      <c r="F715" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>edit_item_fmt</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Edit dialog title; %@ = item name (Android)</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Edit %@</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Editar %@</t>
+        </is>
+      </c>
+      <c r="F716" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>color_channel_red</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Color editor slider label (Android)</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Rojo</t>
+        </is>
+      </c>
+      <c r="F717" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>color_channel_green</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Color editor slider label (Android)</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+      <c r="F718" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>color_channel_blue</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Color editor slider label (Android)</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Azul</t>
+        </is>
+      </c>
+      <c r="F719" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>color_channel_alpha</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Color editor opacity slider label (Android)</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Alpha</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Opacidad</t>
+        </is>
+      </c>
+      <c r="F720" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F720"/>
+  <dimension ref="A1:F728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22149,6 +22149,246 @@
         </is>
       </c>
       <c r="F720" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>deck_selected_count_fmt</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Deck builder: cards picked so far (Android)</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>%d / 5 cards selected</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>%d / 5 cartas seleccionadas</t>
+        </is>
+      </c>
+      <c r="F721" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>deck_card_count_fmt</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Saved deck row: card count (Android)</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>%d / 5 cards</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>%d / 5 cartas</t>
+        </is>
+      </c>
+      <c r="F722" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>hint_fill_empty_columns</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Spider hint when the stock can't be dealt yet (Android shows it as a toast)</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Fill all empty columns before dealing cards.</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>Llena todas las columnas vacías antes de repartir cartas.</t>
+        </is>
+      </c>
+      <c r="F723" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>card_shadow_label</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Custom card colors: shadow swatch (Android)</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Shadow</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>Sombra</t>
+        </is>
+      </c>
+      <c r="F724" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>delete_target_custom_card_back</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Fills Delete %@? for an imported card back (Android)</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>this custom card back</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>este reverso personalizado</t>
+        </is>
+      </c>
+      <c r="F725" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>delete_target_custom_background</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Fills Delete %@? for an imported background (Android)</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>this custom background</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>este fondo personalizado</t>
+        </is>
+      </c>
+      <c r="F726" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>select_image_first_message</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Import screen: Import tapped with no image chosen (Android)</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Please select an image first.</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>Primero selecciona una imagen.</t>
+        </is>
+      </c>
+      <c r="F727" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>import_successful_message</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Import screen: success snackbar (Android)</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Import successful!</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>¡Importación completada!</t>
+        </is>
+      </c>
+      <c r="F728" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F728"/>
+  <dimension ref="A1:F732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22389,6 +22389,126 @@
         </is>
       </c>
       <c r="F728" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>quit_match_confirm_title</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Confirm before quitting a Honeycomb match in progress</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Quit this match?</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>¿Abandonar esta partida?</t>
+        </is>
+      </c>
+      <c r="F729" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Honeycomb</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>quit_match_confirm_body</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Body of the quit-match confirmation</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>It will count as a loss and end your win streak.</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Contará como una derrota y terminará tu racha de victorias.</t>
+        </is>
+      </c>
+      <c r="F730" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>WindowsChrome</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>discard_changes_title</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Windows Options: cancel with unsaved changes</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Discard Changes?</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>¿Descartar cambios?</t>
+        </is>
+      </c>
+      <c r="F731" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>WindowsChrome</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>discard_changes_body</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Windows Options: cancel with unsaved changes</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>You have pending changes which will be lost. Are you sure you want to cancel?</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Tienes cambios pendientes que se perderán. ¿Seguro que quieres cancelar?</t>
+        </is>
+      </c>
+      <c r="F732" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F732"/>
+  <dimension ref="A1:F738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22509,6 +22509,220 @@
         </is>
       </c>
       <c r="F732" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>help_videopoker_subtitle_ios</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Classic draw poker with Jacks or Better, Deuces Wild, and Bonus Poker variants.</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Póker de descarte clásico con las variantes Jacks or Better, Deuces Wild y Bonus Poker.</t>
+        </is>
+      </c>
+      <c r="F733" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>help_videopoker_objective_ios</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Draw the best 5-card poker hand you can. Each variant has its own lowest winning hand.</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Consigue la mejor mano de póker de 5 cartas posible. Cada variante tiene su propia mano ganadora mínima.</t>
+        </is>
+      </c>
+      <c r="F734" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>help_videopoker_how_to_play_ios</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>1. Deal: Tap Deal to receive 5 cards.
+2. Hold: Tap the cards you want to keep.
+3. Draw: Tap Draw. Unheld cards are replaced and your final hand is scored.
+Game Variants:
+• Jacks or Better: The lowest winning hand is a pair of Jacks, Queens, Kings, or Aces.
+• Deuces Wild: All four 2s are wild cards. The lowest winning hand is Three of a Kind.
+• Bonus Poker: Like Jacks or Better, with extra emphasis on Four of a Kind (Four Aces and Four 2s–4s stand out).</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>1. Repartir: Toca Repartir para recibir 5 cartas.
+2. Retener: Toca las cartas que quieras conservar.
+3. Robar: Toca Robar. Las cartas no retenidas se reemplazan y se puntúa tu mano final.
+Variantes:
+• Jacks or Better: La mano ganadora mínima es un par de Jotas, Reinas, Reyes o Ases.
+• Deuces Wild: Los cuatro 2 son comodines. La mano ganadora mínima es un Trío.
+• Bonus Poker: Como Jacks or Better, con especial énfasis en el Póker (destacan Cuatro Ases y Cuatro 2–4).</t>
+        </is>
+      </c>
+      <c r="F735" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>help_videopoker_strategy_ios</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>1. Never Break a Made Hand (Except for 4-to-a-Royal): Only break a Straight or Flush if you are 1 card away from a Royal Flush.
+2. In Deuces Wild, Never Discard a 2: Deuces are wild—always hold every 2 dealt to you!
+3. Nothing Dealt? Hold your high cards (Jack or better) to chase a winning pair.</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>1. Nunca rompas una mano hecha (salvo 4 cartas de Escalera Real): Solo rompe una Escalera o un Color si te falta 1 carta para una Escalera Real.
+2. En Deuces Wild, nunca descartes un 2: ¡Los doses son comodines, retén siempre cada 2!
+3. ¿Sin nada? Retén tus cartas altas (Jota o más) para buscar un par ganador.</t>
+        </is>
+      </c>
+      <c r="F736" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>help_blackjack_rules_ios</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>1. Deal: Tap Deal to start a hand.
+2. Your Turn:
+  – Hit: Take another card.
+  – Stand: Keep your current hand.
+  – Double Down: Take exactly 1 more card and automatically stand. (Available on initial 2 cards with totals of 9, 10, or 11).
+  – Split: If dealt two matching ranks, play them as two separate hands.
+3. Dealer's Turn: Dealer reveals their hidden card and must hit until reaching 17 or higher (stands on all 17s).
+Results: Finish closer to 21 than the dealer without going over to win the hand. A tie is a push.</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>1. Repartir: Toca Repartir para empezar una mano.
+2. Tu turno:
+  – Pedir: Toma otra carta.
+  – Plantarse: Conserva tu mano actual.
+  – Doblar: Toma exactamente 1 carta más y plántate automáticamente. (Disponible con las 2 cartas iniciales si suman 9, 10 u 11).
+  – Dividir: Si recibes dos cartas del mismo rango, juégalas como dos manos separadas.
+3. Turno del crupier: El crupier revela su carta oculta y debe pedir hasta llegar a 17 o más (se planta con cualquier 17).
+Resultados: Termina más cerca de 21 que el crupier sin pasarte para ganar la mano. Un empate es un push.</t>
+        </is>
+      </c>
+      <c r="F737" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>help_blackjack_strategy_ios</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>iOS help/game picker — betting is locked off on iOS (App Store), so no bets, coins, credits, payouts or jackpots</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>1. Always Split Aces and 8s: Never split 10s or 5s.
+2. Double Down on 11: Always Double Down when your starting hand totals 11 against a dealer 2 through 10.
+3. Watch the Dealer's Upcard: If the dealer shows a 2 through 6, they have a high chance of busting—stand on hard 12 or higher and let the dealer draw.</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>1. Divide siempre Ases y 8: Nunca dividas 10 ni 5.
+2. Dobla con 11: Dobla siempre cuando tu mano inicial sume 11 contra un 2 a 10 del crupier.
+3. Observa la carta visible del crupier: Si muestra de 2 a 6, tiene muchas probabilidades de pasarse; plántate con 12 duro o más y deja que el crupier pida.</t>
+        </is>
+      </c>
+      <c r="F738" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F738"/>
+  <dimension ref="A1:F739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14386,8 +14386,8 @@
   – Draw 1 Mode: Clicking the stock reveals 1 card to the waste.
   – Draw 3 Mode: Reveals 3 cards; only the top card of the waste is playable. Once played, the next card in the 3-card batch becomes available.
 • Scoring Modes:
-  – Standard: Flip face-down card (+5 pts) · Waste to Tableau (+5 pts) · Waste/Tableau to Foundation (+10 pts) · Foundation back to Tableau (−15 pts).
-  – Vegas: Start with a debt of −$52. Earn +$5 for every card moved to a foundation. Draw 1 permits only 1 pass through the stock; Draw 3 allows 3 passes (2 redeals).</t>
+  – Standard: Flip face-down card (+5 pts) · Waste to Tableau (+5 pts) · Waste/Tableau to Foundation (+10 pts) · Foundation back to Tableau (−15 pts). Undo takes back a move's points and deducts them again as a penalty. When you win a timed game: −2 pts per 10 seconds played, then a speed bonus of 700,000 ÷ seconds.
+  – Vegas: Start with a debt of −$52. Earn +$5 for every card moved to a foundation (−$5 if one comes back off it). Your bankroll starts at $0 each time you open the game. Draw 1 permits only 1 pass through the stock; Draw 3 allows 3 passes (2 redeals).</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -14398,8 +14398,8 @@
   – Modo Robar 1: Al hacer clic en la pila se revela 1 carta al descarte.
   – Modo Robar 3: Revela 3 cartas; solo la carta superior del descarte es jugable. Una vez jugada, la siguiente carta del grupo de 3 estará disponible.
 • Modos de Puntuación:
-  – Estándar: Voltear carta boca abajo (+5 pts) · Descarte al Tablero (+5 pts) · Descarte/Tablero a la Fundación (+10 pts) · Fundación de vuelta al Tablero (−15 pts).
-  – Vegas: Empiezas con una deuda de −$52. Gana +$5 por cada carta movida a la fundación. Robar 1 permite solo 1 pasada por la pila; Robar 3 permite 3 pasadas (2 repartos extra).</t>
+  – Estándar: Voltear carta boca abajo (+5 pts) · Descarte al Tablero (+5 pts) · Descarte/Tablero a la Fundación (+10 pts) · Fundación de vuelta al Tablero (−15 pts). Deshacer retira los puntos de ese movimiento y los descuenta otra vez como penalización. Al ganar una partida con tiempo: −2 pts por cada 10 segundos jugados, y luego una bonificación de velocidad de 700.000 ÷ segundos.
+  – Vegas: Empiezas con una deuda de −$52. Gana +$5 por cada carta movida a la fundación (−$5 si una vuelve a salir de ella). Tu saldo empieza en $0 cada vez que abres el juego. Robar 1 permite solo 1 pasada por la pila; Robar 3 permite 3 pasadas (2 repartos extra).</t>
         </is>
       </c>
       <c r="F465" t="b">
@@ -14555,7 +14555,8 @@
           <t>• Tableau Building: Stack cards in descending rank and alternating colors.
 • Free Cell Storage: Each free cell can hold exactly 1 card at a time.
 • Multi-Card Movement Capacity: You can move a face-up card sequence in a single action. The maximum number of cards you can move at once is calculated as: (Free Cells Available + 1) × 2^(Empty Tableau Columns).
-• Empty Columns: Any single card or valid sequence can be moved into an empty tableau column.</t>
+• Empty Columns: Any single card or valid sequence can be moved into an empty tableau column — but the column you're moving into doesn't count toward the capacity above.
+• Scoring: +10 for each card moved to a foundation, −15 for taking one back off.</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
@@ -14563,7 +14564,8 @@
           <t>• Construcción del Tablero: Apila cartas en rango descendente y colores alternos.
 • Almacenamiento en Celdas Libres: Cada celda libre puede contener exactamente 1 carta a la vez.
 • Capacidad de Movimiento Múltiple: Puedes mover una secuencia de cartas boca arriba en una sola acción. El número máximo de cartas que puedes mover a la vez se calcula como: (Celdas Libres Disponibles + 1) × 2^(Columnas Vacías en el Tablero).
-• Columnas Vacías: Cualquier carta individual o secuencia válida se puede mover a una columna vacía en el tablero.</t>
+• Columnas Vacías: Cualquier carta individual o secuencia válida se puede mover a una columna vacía en el tablero, pero la columna a la que mueves no cuenta para la capacidad de arriba.
+• Puntuación: +10 por cada carta movida a una fundación, −15 por retirar una de ella.</t>
         </is>
       </c>
       <c r="F470" t="b">
@@ -14689,7 +14691,8 @@
   – 2-Suits (Medium): 52 Spades and 52 Hearts.
   – 4-Suits (Hard): All four standard suits are used.
 • Tableau Building: Stack cards in descending rank regardless of suit (e.g., a 7 of Hearts can sit on an 8 of Spades). Crucial Exception: You may only move a multi-card sequence if all cards in that sequence share the same suit.
-• Stock Deals: Click the stock to deal 1 card onto every tableau column. Requirement: Every column must contain at least 1 card before you can deal from the stock.</t>
+• Stock Deals: Click the stock to deal 1 card onto every tableau column. Requirement: Every column must contain at least 1 card before you can deal from the stock.
+• Scoring: You start with 500 points; every move or deal costs 1 point, and each completed King-to-Ace run earns 100.</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
@@ -14699,7 +14702,8 @@
   – 2 Palos (Medio): 52 Picas y 52 Corazones.
   – 4 Palos (Difícil): Se usan los cuatro palos estándar.
 • Construcción del Tablero: Apila cartas en rango descendente sin importar el palo (ej., un 7 de Corazones puede colocarse sobre un 8 de Picas). Excepción Crucial: Solo puedes mover una secuencia de múltiples cartas si todas las cartas de esa secuencia comparten el mismo palo.
-• Repartos desde la Pila: Haz clic en la pila para repartir 1 carta en cada columna del tablero. Requisito: Cada columna debe contener al menos 1 carta antes de que puedas repartir desde la pila.</t>
+• Repartos desde la Pila: Haz clic en la pila para repartir 1 carta en cada columna del tablero. Requisito: Cada columna debe contener al menos 1 carta antes de que puedas repartir desde la pila.
+• Puntuación: Empiezas con 500 puntos; cada movimiento o reparto cuesta 1 punto, y cada secuencia completa de Rey a As suma 100.</t>
         </is>
       </c>
       <c r="F474" t="b">
@@ -14924,31 +14928,31 @@
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>1. Place Bet &amp; Deal: Select your chip wager (1, 5, 10, 25) or press Bet Max (M), then press Deal (Space).
+          <t>1. Place Bet &amp; Deal: Build your bet with the chips (1, 5, 10, 25 — or 2X to double it), then press Deal (Space).
 2. Your Turn:
   – Hit (H): Take another card.
   – Stand (S): Keep your current hand.
   – Double Down (D): Double your wager, receive exactly 1 card, and automatically stand. (Available on initial 2 cards with totals of 9, 10, or 11).
-  – Split (P): If dealt two matching ranks, split them into two separate hands (requires an equal second wager).
-3. Dealer's Turn: Dealer reveals their hidden card and must hit until reaching 17 or higher (stands on all 17s).
+  – Split (P): If dealt two matching ranks, split them into two separate hands (requires an equal second wager). One split per round; split Aces get exactly one more card each.
+3. Dealer's Turn: Dealer reveals their hidden card and must hit until reaching 17 or higher (stands on all 17s). If every one of your hands has busted, or you have a natural, the dealer just reveals and doesn't draw. A dealer natural is checked as soon as the cards are dealt — it beats everything except your own natural (a push).
 Payout Schedule:
 • Standard Win: 1:1 payout.
-• Natural Blackjack (Ace + 10-value card): 3:1 payout.
+• Natural Blackjack (Ace + 10-value card, on an unsplit hand): 3:1 payout.
 • Push (Tie): Bet is returned.</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>1. Haz Apuesta y Reparte: Selecciona tu apuesta en fichas (1, 5, 10, 25) o presiona Apuesta Máxima (M), luego presiona Repartir (Espacio).
+          <t>1. Haz Apuesta y Reparte: Arma tu apuesta con las fichas (1, 5, 10, 25, o 2X para duplicarla), luego presiona Repartir (Espacio).
 2. Tu Turno:
   – Pedir (H): Toma otra carta.
   – Plantarse (S): Mantén tu mano actual.
   – Doblar (D): Dobla tu apuesta, recibe exactamente 1 carta, y te plantas automáticamente. (Disponible en las 2 cartas iniciales con un total de 9, 10, u 11).
-  – Dividir (P): Si se te reparten dos rangos iguales, divídelos en dos manos separadas (requiere una segunda apuesta igual).
-3. Turno del Repartidor: El repartidor revela su carta oculta y debe pedir hasta alcanzar 17 o más (se planta en todos los 17s).
+  – Dividir (P): Si se te reparten dos rangos iguales, divídelos en dos manos separadas (requiere una segunda apuesta igual). Una división por ronda; los Ases divididos reciben exactamente una carta más cada uno.
+3. Turno del Repartidor: El repartidor revela su carta oculta y debe pedir hasta alcanzar 17 o más (se planta en todos los 17s). Si todas tus manos se pasaron, o tienes un natural, el repartidor solo revela su carta y no pide. El natural del repartidor se revisa en cuanto se reparten las cartas: gana a todo excepto a tu propio natural (empate).
 Esquema de Pagos:
 • Ganancia Estándar: pago 1:1.
-• Blackjack Natural (As + carta de valor 10): pago 3:1.
+• Blackjack Natural (As + carta de valor 10, en una mano sin dividir): pago 3:1.
 • Empate (Push): Se devuelve la apuesta.</t>
         </is>
       </c>
@@ -15038,12 +15042,12 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Battle an AI opponent on a 3×3 grid using a 5-card deck. Each card features 4 directional stats (Top, Right, Bottom, Left). Place cards strategically to flip enemy cards to your color. Whoever controls the majority of the 9 grid cells at the end wins!</t>
+          <t>Battle an AI opponent on a 3×3 grid using a 5-card deck. Each card features 4 directional stats (Top, Right, Bottom, Left). Place cards strategically to flip enemy cards to your color. When the grid is full, each side scores the cards they own on the board plus any still in hand — the higher score wins!</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Lucha contra un oponente de la IA en una cuadrícula de 3×3 usando un mazo de 5 cartas. Cada carta cuenta con 4 estadísticas direccionales (Arriba, Derecha, Abajo, Izquierda). Coloca las cartas estratégicamente para voltear las cartas enemigas a tu color. ¡Quien controle la mayoría de las 9 celdas al final gana!</t>
+          <t>Lucha contra un oponente de la IA en una cuadrícula de 3×3 usando un mazo de 5 cartas. Cada carta cuenta con 4 estadísticas direccionales (Arriba, Derecha, Abajo, Izquierda). Coloca las cartas estratégicamente para voltear las cartas enemigas a tu color. Cuando la cuadrícula se llena, cada lado suma las cartas que controla en el tablero más las que aún tiene en la mano: ¡gana la puntuación más alta!</t>
         </is>
       </c>
       <c r="F484" t="b">
@@ -15069,13 +15073,13 @@
       <c r="D485" t="inlineStr">
         <is>
           <t>• Capturing: When you place a card adjacent to an opponent's card, your facing stat is compared against their opposite facing stat. If your stat is higher, the enemy card is captured (flipped to your color). Stat 10 is rendered as "A".
-• Hive Minds: A card captured during a turn immediately checks its own adjacent neighbors, triggering a chain-reaction capture sequence!</t>
+• Hive Minds: When Symmetry or Math Bee captures cards, each of those captured cards then attacks its own neighbors as if it had just been placed — which can set off a chain reaction of captures! (An ordinary higher-stat capture doesn't start a chain.)</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
           <t>• Capturas: Cuando colocas una carta adyacente a la de un oponente, tu estadística de cara se compara con su estadística de cara opuesta. Si tu estadística es mayor, la carta enemiga es capturada (volteada a tu color). La estadística 10 se representa como "A".
-• Mentes Colmena: ¡Una carta capturada durante un turno revisa de inmediato a sus propios vecinos adyacentes, desencadenando una secuencia de captura en reacción en cadena!</t>
+• Mentes Colmena: Cuando Simetría o Abeja Matemática capturan cartas, cada carta capturada ataca a sus propios vecinos como si acabara de colocarse, ¡lo que puede desatar una reacción en cadena de capturas! (Una captura normal por estadística mayor no inicia una cadena.)</t>
         </is>
       </c>
       <c r="F485" t="b">
@@ -15100,7 +15104,7 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>• Steal Mechanics: After winning a match, double-click an eligible dealer card to permanently steal it into your Card Bank! Only one steal is allowed per match.
+          <t>• Steal Mechanics: After winning a match, choose Steal a Card, then double-click (double-tap on phones) one of the opponent's cards you captured to add it to your Card Bank for good! Only one steal is allowed per match.
 • Deck Rarity Caps: Custom decks are limited to: at most one 5★ card, and at most one 4★ card if a 5★ is present (or up to two 4★ cards without a 5★).
 • Smart Opponent Decks: The AI automatically selects decks containing cards you don't yet own to maximize steal rewards.
 • Steal Protection: Stuck in a Rematch chain against an opponent whose cards you just can't seem to capture? Win two Rematches in a row against the same opponent with nothing eligible to steal, and any not-yet-unlocked card left on the board becomes stealable on that second win — captured or not. Once triggered, it stays active for the rest of that Rematch chain, so every future win keeps offering a steal — you won't have to re-earn it. Starting a fresh New Game (a new opponent) is what turns it back off.</t>
@@ -15108,7 +15112,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>• Mecánica de Robo: Después de ganar una partida, ¡haz doble clic en una carta elegible del repartidor para robarla permanentemente hacia tu Banco de Cartas! Solo se permite un robo por partida.
+          <t>• Mecánica de Robo: Después de ganar una partida, elige Roba una Carta y haz doble clic (doble toque en el teléfono) en una de las cartas del oponente que capturaste, ¡para añadirla a tu Banco de Cartas para siempre! Solo se permite un robo por partida.
 • Límites de Rareza de Mazo: Los mazos personalizados están limitados a: como máximo una carta de 5★, y como máximo una carta de 4★ si hay una de 5★ presente (o hasta dos cartas de 4★ sin una de 5★).
 • Mazos de Oponente Inteligentes: La IA selecciona automáticamente mazos que contienen cartas que aún no tienes para maximizar las recompensas de robo.
 • Protección Anti-Robo: ¿Atrapado en una cadena de Revanchas contra un oponente cuyas cartas parece que no puedes capturar? Gana dos Revanchas seguidas contra el mismo oponente sin que haya nada elegible para robar, y cualquier carta aún no desbloqueada que quede en el tablero se vuelve robable en esa segunda victoria — capturada o no. Una vez activada, se mantiene activa para el resto de esa cadena de Revanchas, para que cada victoria futura siga ofreciendo un robo — no tendrás que volver a ganarlo. Esto se desactiva al comenzar una Nueva Partida (contra un nuevo oponente).</t>
@@ -15136,12 +15140,12 @@
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Enabling No Stress Mode in Options supplies you with a fixed strong deck every match and hides the Card Steal mechanics.</t>
+          <t>Enabling No Stress Mode in Options deals you a random strong deck every match and hides the Card Steal mechanics.</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Activar el Modo Sin Estrés en Opciones te proporciona un mazo fuerte fijo en cada partida y oculta las mecánicas de Robo de Cartas.</t>
+          <t>Activar el Modo Sin Estrés en Opciones te reparte un mazo fuerte al azar en cada partida y oculta las mecánicas de Robo de Cartas.</t>
         </is>
       </c>
       <c r="F487" t="b">
@@ -22671,8 +22675,8 @@
   – Hit: Take another card.
   – Stand: Keep your current hand.
   – Double Down: Take exactly 1 more card and automatically stand. (Available on initial 2 cards with totals of 9, 10, or 11).
-  – Split: If dealt two matching ranks, play them as two separate hands.
-3. Dealer's Turn: Dealer reveals their hidden card and must hit until reaching 17 or higher (stands on all 17s).
+  – Split: If dealt two matching ranks, play them as two separate hands. One split per round; split Aces get exactly one more card each.
+3. Dealer's Turn: Dealer reveals their hidden card and must hit until reaching 17 or higher (stands on all 17s). If every one of your hands has busted, or you have a natural (Ace + 10-value card on an unsplit hand), the dealer just reveals and doesn't draw. A dealer natural is checked as soon as the cards are dealt.
 Results: Finish closer to 21 than the dealer without going over to win the hand. A tie is a push.</t>
         </is>
       </c>
@@ -22683,8 +22687,8 @@
   – Pedir: Toma otra carta.
   – Plantarse: Conserva tu mano actual.
   – Doblar: Toma exactamente 1 carta más y plántate automáticamente. (Disponible con las 2 cartas iniciales si suman 9, 10 u 11).
-  – Dividir: Si recibes dos cartas del mismo rango, juégalas como dos manos separadas.
-3. Turno del crupier: El crupier revela su carta oculta y debe pedir hasta llegar a 17 o más (se planta con cualquier 17).
+  – Dividir: Si recibes dos cartas del mismo rango, juégalas como dos manos separadas. Una división por ronda; los Ases divididos reciben exactamente una carta más cada uno.
+3. Turno del crupier: El crupier revela su carta oculta y debe pedir hasta llegar a 17 o más (se planta con cualquier 17). Si todas tus manos se pasaron, o tienes un natural (As + carta de valor 10 en una mano sin dividir), el crupier solo revela su carta y no pide. El natural del crupier se revisa en cuanto se reparten las cartas.
 Resultados: Termina más cerca de 21 que el crupier sin pasarte para ganar la mano. Un empate es un push.</t>
         </is>
       </c>
@@ -22723,6 +22727,46 @@
         </is>
       </c>
       <c r="F738" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>help_klondike_rules_ios</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>iOS Klondike rules — no Vegas scoring (betting-style; removed on iOS for the App Store)</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>• Tableau Building: Stack cards in descending rank with alternating colors (e.g., a red 6 on a black 7). You may move a single card or an entire face-up sequence to another column.
+• Empty Columns: Only a King (or a sequence starting with a King) may be placed in an empty tableau column.
+• Stock &amp; Waste:
+  – Draw 1 Mode: Clicking the stock reveals 1 card to the waste.
+  – Draw 3 Mode: Reveals 3 cards; only the top card of the waste is playable. Once played, the next card in the 3-card batch becomes available.
+• Scoring: Flip face-down card (+5 pts) · Waste to Tableau (+5 pts) · Waste/Tableau to Foundation (+10 pts) · Foundation back to Tableau (−15 pts). Undo takes back a move's points and deducts them again as a penalty. When you win a timed game: −2 pts per 10 seconds played, then a speed bonus of 700,000 ÷ seconds.</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>• Construcción del Tablero: Apila cartas en rango descendente alternando colores (ej., un 6 rojo sobre un 7 negro). Puedes mover una sola carta o una secuencia entera boca arriba a otra columna.
+• Columnas Vacías: Solo un Rey (o una secuencia que empiece con un Rey) puede colocarse en una columna vacía del tablero.
+• Pila y Descarte:
+  – Modo Robar 1: Al hacer clic en la pila se revela 1 carta al descarte.
+  – Modo Robar 3: Revela 3 cartas; solo la carta superior del descarte es jugable. Una vez jugada, la siguiente carta del grupo de 3 estará disponible.
+• Puntuación: Voltear carta boca abajo (+5 pts) · Descarte al Tablero (+5 pts) · Descarte/Tablero a la Fundación (+10 pts) · Fundación de vuelta al Tablero (−15 pts). Deshacer retira los puntos de ese movimiento y los descuenta otra vez como penalización. Al ganar una partida con tiempo: −2 pts por cada 10 segundos jugados, y luego una bonificación de velocidad de 700.000 ÷ segundos.</t>
+        </is>
+      </c>
+      <c r="F739" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F739"/>
+  <dimension ref="A1:F740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22767,6 +22767,36 @@
         </is>
       </c>
       <c r="F739" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>HelpIOS</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>help_klondike_subtitle_ios</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Klondike one-liner on mobile (iOS/Android) — no Vegas scoring there</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Classic single-deck solitaire with Draw 1 and Draw 3 modes.</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Clásico solitario de un mazo con modos Robar 1 y Robar 3.</t>
+        </is>
+      </c>
+      <c r="F740" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F740"/>
+  <dimension ref="A1:F745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22797,6 +22797,156 @@
         </is>
       </c>
       <c r="F740" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>err_deck_needs_5_cards</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Deck validation error, Windows Honeycomb deck builder</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>A deck must contain exactly 5 cards.</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Un mazo debe contener exactamente 5 cartas.</t>
+        </is>
+      </c>
+      <c r="F741" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>err_name_empty</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Deck validation error, Windows Honeycomb deck builder</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Deck name cannot be empty.</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>El nombre del mazo no puede estar vacío.</t>
+        </is>
+      </c>
+      <c r="F742" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>a11y_recycle</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Android screen-reader label on the Klondike stock-pile recycle icon</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Recycle</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Reciclar</t>
+        </is>
+      </c>
+      <c r="F743" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>a11y_decrease</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Android screen-reader label on the options stepper minus button</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Decrease</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Disminuir</t>
+        </is>
+      </c>
+      <c r="F744" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>AndroidChrome</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>a11y_increase</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Android screen-reader label on the options stepper plus button</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Aumentar</t>
+        </is>
+      </c>
+      <c r="F745" t="b">
         <v>1</v>
       </c>
     </row>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -4562,12 +4562,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Video Poker Help</t>
+          <t>Draw Poker Help</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ayuda de Video Póker</t>
+          <t>Ayuda de Póker de Descarte</t>
         </is>
       </c>
       <c r="F138" t="b">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Video Poker Statistics</t>
+          <t>Draw Poker Statistics</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Estadísticas de Video Póker</t>
+          <t>Estadísticas de Póker de Descarte</t>
         </is>
       </c>
       <c r="F338" t="b">
@@ -15420,12 +15420,12 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Video Poker</t>
+          <t>Draw Poker</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Video Póker</t>
+          <t>Póker de Descarte</t>
         </is>
       </c>
       <c r="F496" t="b">
@@ -17610,12 +17610,12 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>VIDEO POKER</t>
+          <t>DRAW POKER</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>VIDEO POKER</t>
+          <t>PÓKER DE DESCARTE</t>
         </is>
       </c>
       <c r="F569" t="b">
@@ -22991,7 +22991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F288"/>
+  <dimension ref="A1:F287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31519,7 +31519,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Get rich or buzz trying.</t>
+          <t>To bee, or not to bee... wait, whose turn is it?</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>To bee, or not to bee... wait, whose turn is it?</t>
+          <t>May the swarm be with you.</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -31566,7 +31566,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>No Translation</t>
+          <t>Que el enjambre te acompañe.</t>
         </is>
       </c>
     </row>
@@ -31583,7 +31583,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>May the swarm be with you.</t>
+          <t>Live, Laugh, Pollinate.</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Que el enjambre te acompañe.</t>
+          <t>Vive, Ríe, Poliniza.</t>
         </is>
       </c>
     </row>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Live, Laugh, Pollinate.</t>
+          <t>Keep calm and buzz on.</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -31630,7 +31630,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vive, Ríe, Poliniza.</t>
+          <t>No Translation</t>
         </is>
       </c>
     </row>
@@ -31647,7 +31647,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Keep calm and buzz on.</t>
+          <t>Home is where the hive is.</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -31662,7 +31662,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>No Translation</t>
+          <t>El hogar está donde está la colmena.</t>
         </is>
       </c>
     </row>
@@ -31679,7 +31679,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Home is where the hive is.</t>
+          <t>Just a worker bee looking for my queen.</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -31694,7 +31694,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>El hogar está donde está la colmena.</t>
+          <t>Solo una abeja obrera buscando a mi reina.</t>
         </is>
       </c>
     </row>
@@ -31711,7 +31711,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Just a worker bee looking for my queen.</t>
+          <t>Are you gonna play a card, or just sit there looking sweet?</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Solo una abeja obrera buscando a mi reina.</t>
+          <t>¿Vas a jugar una carta, o solo te vas a sentar ahí luciendo dulce?</t>
         </is>
       </c>
     </row>
@@ -31743,7 +31743,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Are you gonna play a card, or just sit there looking sweet?</t>
+          <t>Frankly, my dear, I don't give a buzz.</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -31758,7 +31758,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>¿Vas a jugar una carta, o solo te vas a sentar ahí luciendo dulce?</t>
+          <t>No Translation</t>
         </is>
       </c>
     </row>
@@ -31775,7 +31775,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Frankly, my dear, I don't give a buzz.</t>
+          <t>We're gonna need a bigger hive.</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -31790,7 +31790,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>No Translation</t>
+          <t>Vamos a necesitar una colmena más grande.</t>
         </is>
       </c>
     </row>
@@ -31807,7 +31807,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>We're gonna need a bigger hive.</t>
+          <t>Show me the honey!</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -31822,7 +31822,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Vamos a necesitar una colmena más grande.</t>
+          <t>¡Muéstrame la miel!</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Show me the honey!</t>
+          <t>I'll bee back.</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -31854,7 +31854,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>¡Muéstrame la miel!</t>
+          <t>No Translation</t>
         </is>
       </c>
     </row>
@@ -31871,7 +31871,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>I'll bee back.</t>
+          <t>Nobody puts Baby Bee in a corner.</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -31886,7 +31886,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>No Translation</t>
+          <t>Nadie pone a Abeja Bebé en un rincón.</t>
         </is>
       </c>
     </row>
@@ -31903,7 +31903,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Nobody puts Baby Bee in a corner.</t>
+          <t>Sweet dreams are made of bees.</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -31918,7 +31918,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Nadie pone a Abeja Bebé en un rincón.</t>
+          <t>No Translation</t>
         </is>
       </c>
     </row>
@@ -31935,7 +31935,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Sweet dreams are made of bees.</t>
+          <t>Bee yourself; everyone else is already taken.</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -31967,7 +31967,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bee yourself; everyone else is already taken.</t>
+          <t>Mind your own beeswax!</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -31999,7 +31999,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Mind your own beeswax!</t>
+          <t>This one weird trick captures 4 cards at once — dealers don't want you to know it.</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -32014,7 +32014,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>No Translation</t>
+          <t>Este extraño truco captura 4 cartas a la vez — los repartidores no quieren que lo sepas.</t>
         </is>
       </c>
     </row>
@@ -32031,7 +32031,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>This one weird trick captures 4 cards at once — dealers don't want you to know it.</t>
+          <t>You won't believe what happened when a worker bee met a Fallen Ace.</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -32046,7 +32046,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Este extraño truco captura 4 cartas a la vez — los repartidores no quieren que lo sepas.</t>
+          <t>No vas a creer lo que pasó cuando una abeja obrera conoció a un As Caído.</t>
         </is>
       </c>
     </row>
@@ -32063,7 +32063,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>You won't believe what happened when a worker bee met a Fallen Ace.</t>
+          <t>She said yes to Symmetry. He said yes to Math Bee. Chaos ensued.</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -32078,29 +32078,29 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>No vas a creer lo que pasó cuando una abeja obrera conoció a un As Caído.</t>
+          <t>Ella dijo sí a la Simetría. Él dijo sí a Abeja Matemática. Se desató el caos.</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Idle Action</t>
+          <t>Gameplay</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>No action taken for one minute.</t>
+          <t>Player runs out of credits (Video Poker/Blackjack).</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>She said yes to Symmetry. He said yes to Math Bee. Chaos ensued.</t>
+          <t>Busy as a bee, broke as a beekeeper.</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Ambiance</t>
+          <t>Repeatable Flavor</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -32110,29 +32110,29 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Ella dijo sí a la Simetría. Él dijo sí a Abeja Matemática. Se desató el caos.</t>
+          <t>Ocupado como una abeja, arruinado como un apicultor.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Gameplay</t>
+          <t>Idle Action</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Player runs out of credits (Video Poker/Blackjack).</t>
+          <t>No action taken for one minute.</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Busy as a bee, broke as a beekeeper.</t>
+          <t>Absence makes the heart grow fonder — and the hive grow louder.</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Repeatable Flavor</t>
+          <t>Ambiance</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -32142,7 +32142,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Ocupado como una abeja, arruinado como un apicultor.</t>
+          <t>La ausencia hace que el corazón se encariñe — y la colmena suene más fuerte.</t>
         </is>
       </c>
     </row>
@@ -32159,7 +32159,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Absence makes the heart grow fonder — and the hive grow louder.</t>
+          <t>Two bees or not two bees — that's a math problem, not a question.</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -32173,38 +32173,6 @@
         </is>
       </c>
       <c r="F287" t="inlineStr">
-        <is>
-          <t>La ausencia hace que el corazón se encariñe — y la colmena suene más fuerte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Idle Action</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr">
-        <is>
-          <t>No action taken for one minute.</t>
-        </is>
-      </c>
-      <c r="C288" t="inlineStr">
-        <is>
-          <t>Two bees or not two bees — that's a math problem, not a question.</t>
-        </is>
-      </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>Ambiance</t>
-        </is>
-      </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>Toast</t>
-        </is>
-      </c>
-      <c r="F288" t="inlineStr">
         <is>
           <t>No Translation</t>
         </is>

--- a/tools/Honeycomb_Localization.xlsx
+++ b/tools/Honeycomb_Localization.xlsx
@@ -17040,12 +17040,12 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>If the match ends in a draw, a rematch begins immediately.</t>
+          <t>If the match ends in a draw, the cards currently owned by each player become their new hand and the match restarts immediately.</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Si la partida termina en empate, comienza una revancha inmediatamente.</t>
+          <t>Si la partida termina en empate, las cartas que posee cada jugador en ese momento se convierten en su nueva mano y la partida se reinicia de inmediato.</t>
         </is>
       </c>
       <c r="F550" t="b">
